--- a/files/九龙-将军澳-海瑅湾 I.xlsx
+++ b/files/九龙-将军澳-海瑅湾 I.xlsx
@@ -30504,7 +30504,7 @@
       </c>
       <c r="G463" s="3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="H463" s="5" t="n">
@@ -79356,7 +79356,7 @@
       </c>
       <c r="G1237" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H1237" s="5" t="n">
@@ -86000,7 +86000,7 @@
           <t>C | 584呎 (2房)
 $1062万
 $18,191/呎
-(26年-08月-23日)</t>
+(26年-09月-07日)</t>
         </is>
       </c>
       <c r="E33" s="23" t="inlineStr">
@@ -93416,7 +93416,7 @@
           <t>B | 628呎 (3房)
 $1184万
 $18,854/呎
-(26年-08月-19日)</t>
+(26年-09月-04日)</t>
         </is>
       </c>
       <c r="D55" s="20" t="inlineStr">

--- a/files/九龙-将军澳-海瑅湾 I.xlsx
+++ b/files/九龙-将军澳-海瑅湾 I.xlsx
@@ -11865,38 +11865,30 @@
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H172" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I172" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H172" s="5" t="n">
+        <v>18034000</v>
+      </c>
+      <c r="I172" s="5" t="n">
+        <v>21092</v>
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K172" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L172" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K172" s="5" t="n">
+        <v>18034000</v>
+      </c>
+      <c r="L172" s="5" t="n">
+        <v>21092</v>
       </c>
       <c r="M172" s="3" t="inlineStr">
         <is>
@@ -11905,7 +11897,7 @@
       </c>
       <c r="N172" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -31310,7 +31302,7 @@
       </c>
       <c r="G476" s="3" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H476" s="5" t="n">
@@ -31801,34 +31793,34 @@
       </c>
       <c r="F484" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G484" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="H484" s="5" t="n">
-        <v>12460000</v>
+        <v>10840200</v>
       </c>
       <c r="I484" s="5" t="n">
-        <v>21336</v>
+        <v>18562</v>
       </c>
       <c r="J484" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K484" s="5" t="n">
-        <v>10591000</v>
+        <v>10840200</v>
       </c>
       <c r="L484" s="5" t="n">
-        <v>18135</v>
+        <v>18562</v>
       </c>
       <c r="M484" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N484" s="3" t="inlineStr">
@@ -33041,23 +33033,23 @@
       </c>
       <c r="F504" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G504" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="H504" s="5" t="n">
-        <v>9572000</v>
+        <v>8136200</v>
       </c>
       <c r="I504" s="5" t="n">
-        <v>20674</v>
+        <v>17573</v>
       </c>
       <c r="J504" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K504" s="5" t="n">
@@ -33068,7 +33060,7 @@
       </c>
       <c r="M504" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N504" s="3" t="inlineStr">
@@ -33480,7 +33472,7 @@
       </c>
       <c r="G511" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H511" s="5" t="n">
@@ -81048,14 +81040,14 @@
       </c>
       <c r="G1263" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H1263" s="5" t="n">
-        <v>7309100</v>
+        <v>7039100</v>
       </c>
       <c r="I1263" s="5" t="n">
-        <v>17655</v>
+        <v>17003</v>
       </c>
       <c r="J1263" s="3" t="inlineStr">
         <is>
@@ -81063,10 +81055,10 @@
         </is>
       </c>
       <c r="K1263" s="5" t="n">
-        <v>7309100</v>
+        <v>7039100</v>
       </c>
       <c r="L1263" s="5" t="n">
-        <v>17655</v>
+        <v>17003</v>
       </c>
       <c r="M1263" s="3" t="inlineStr">
         <is>
@@ -81486,7 +81478,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>81</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -81496,7 +81488,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>126</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -83162,12 +83154,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C42" s="23" t="inlineStr">
+      <c r="C42" s="22" t="inlineStr">
         <is>
           <t>B | 855呎 (3房)
-招标单位
--
-(在售)</t>
+$1803万
+$21,092/呎
+(26年-09月-07日)</t>
         </is>
       </c>
       <c r="D42" s="20" t="inlineStr">
@@ -84117,7 +84109,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>101</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -84127,7 +84119,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>285</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -86136,7 +86128,7 @@
           <t>D | 463呎 (2房)
 $820万
 $17,712/呎
-(26年-08月-16日)</t>
+(26年-09月-09日)</t>
         </is>
       </c>
       <c r="F35" s="22" t="inlineStr">
@@ -86187,12 +86179,12 @@
 (26年-05月-08日)</t>
         </is>
       </c>
-      <c r="D36" s="23" t="inlineStr">
+      <c r="D36" s="22" t="inlineStr">
         <is>
           <t>C | 584呎 (2房)
-$1246万
-$21,336/呎
-(在售)</t>
+$1084万
+$18,562/呎
+(26年-09月-07日)</t>
         </is>
       </c>
       <c r="E36" s="23" t="inlineStr">
@@ -86387,12 +86379,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E39" s="23" t="inlineStr">
+      <c r="E39" s="22" t="inlineStr">
         <is>
           <t>D | 463呎 (2房)
-$957万
-$20,674/呎
-(在售)</t>
+$814万
+$17,573/呎
+(26年-09月-07日)</t>
         </is>
       </c>
       <c r="F39" s="22" t="inlineStr">
@@ -86456,7 +86448,7 @@
           <t>D | 463呎 (2房)
 $812万
 $17,538/呎
-(26年-08月-24日)</t>
+(26年-09月-09日)</t>
         </is>
       </c>
       <c r="F40" s="22" t="inlineStr">
@@ -93721,9 +93713,9 @@
       <c r="G60" s="22" t="inlineStr">
         <is>
           <t>F | 414呎 (2房)
-$731万
-$17,655/呎
-(26年-08月-24日)</t>
+$704万
+$17,003/呎
+(26年-09月-10日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-将军澳-海瑅湾 I.xlsx
+++ b/files/九龙-将军澳-海瑅湾 I.xlsx
@@ -12261,38 +12261,30 @@
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H178" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I178" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="H178" s="5" t="n">
+        <v>20124000</v>
+      </c>
+      <c r="I178" s="5" t="n">
+        <v>22586</v>
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K178" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L178" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K178" s="5" t="n">
+        <v>20124000</v>
+      </c>
+      <c r="L178" s="5" t="n">
+        <v>22586</v>
       </c>
       <c r="M178" s="3" t="inlineStr">
         <is>
@@ -12301,7 +12293,7 @@
       </c>
       <c r="N178" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -32227,34 +32219,34 @@
       </c>
       <c r="F491" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G491" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="H491" s="5" t="n">
-        <v>12435000</v>
+        <v>10569700</v>
       </c>
       <c r="I491" s="5" t="n">
-        <v>21293</v>
+        <v>18099</v>
       </c>
       <c r="J491" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K491" s="5" t="n">
-        <v>10569750</v>
+        <v>10569700</v>
       </c>
       <c r="L491" s="5" t="n">
         <v>18099</v>
       </c>
       <c r="M491" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N491" s="3" t="inlineStr">
@@ -57636,7 +57628,7 @@
       </c>
       <c r="G897" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H897" s="5" t="n">
@@ -81478,7 +81470,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -81488,7 +81480,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>127</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -83193,12 +83185,12 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B43" s="23" t="inlineStr">
+      <c r="B43" s="22" t="inlineStr">
         <is>
           <t>A | 891呎 (3房)
-招标单位
--
-(在售)</t>
+$2012万
+$22,586/呎
+(26年-09月-11日)</t>
         </is>
       </c>
       <c r="C43" s="23" t="inlineStr">
@@ -84109,7 +84101,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -84119,7 +84111,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>286</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -86243,12 +86235,12 @@
 (26年-05月-08日)</t>
         </is>
       </c>
-      <c r="D37" s="23" t="inlineStr">
+      <c r="D37" s="22" t="inlineStr">
         <is>
           <t>C | 584呎 (2房)
-$1244万
-$21,293/呎
-(在售)</t>
+$1057万
+$18,099/呎
+(26年-09月-12日)</t>
         </is>
       </c>
       <c r="E37" s="23" t="inlineStr">
@@ -90154,7 +90146,7 @@
           <t>B | 599呎 (2房)
 $1140万
 $19,025/呎
-(26年-08月-19日)</t>
+(26年-09月-11日)</t>
         </is>
       </c>
       <c r="D53" s="22" t="inlineStr">

--- a/files/九龙-将军澳-海瑅湾 I.xlsx
+++ b/files/九龙-将军澳-海瑅湾 I.xlsx
@@ -33087,23 +33087,23 @@
       </c>
       <c r="F505" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G505" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H505" s="5" t="n">
-        <v>12386000</v>
+        <v>10528100</v>
       </c>
       <c r="I505" s="5" t="n">
-        <v>21209</v>
+        <v>18028</v>
       </c>
       <c r="J505" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K505" s="5" t="n">
@@ -33114,7 +33114,7 @@
       </c>
       <c r="M505" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N505" s="3" t="inlineStr">
@@ -39163,23 +39163,23 @@
       </c>
       <c r="F603" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G603" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H603" s="5" t="n">
-        <v>12020000</v>
+        <v>10217000</v>
       </c>
       <c r="I603" s="5" t="n">
-        <v>20582</v>
+        <v>17495</v>
       </c>
       <c r="J603" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K603" s="5" t="n">
@@ -39190,7 +39190,7 @@
       </c>
       <c r="M603" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N603" s="3" t="inlineStr">
@@ -47361,38 +47361,30 @@
       </c>
       <c r="F732" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G732" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H732" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I732" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H732" s="5" t="n">
+        <v>11712000</v>
+      </c>
+      <c r="I732" s="5" t="n">
+        <v>19553</v>
       </c>
       <c r="J732" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K732" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L732" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K732" s="5" t="n">
+        <v>11712000</v>
+      </c>
+      <c r="L732" s="5" t="n">
+        <v>19553</v>
       </c>
       <c r="M732" s="3" t="inlineStr">
         <is>
@@ -47401,7 +47393,7 @@
       </c>
       <c r="N732" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -78564,7 +78556,7 @@
       </c>
       <c r="G1225" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H1225" s="5" t="n">
@@ -84101,7 +84093,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>98</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -84111,7 +84103,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>288</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -86363,12 +86355,12 @@
 (26年-04月-28日)</t>
         </is>
       </c>
-      <c r="D39" s="23" t="inlineStr">
+      <c r="D39" s="22" t="inlineStr">
         <is>
           <t>C | 584呎 (2房)
-$1239万
-$21,209/呎
-(在售)</t>
+$1053万
+$18,028/呎
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="E39" s="22" t="inlineStr">
@@ -87259,12 +87251,12 @@
 (26年-04月-29日)</t>
         </is>
       </c>
-      <c r="D53" s="23" t="inlineStr">
+      <c r="D53" s="22" t="inlineStr">
         <is>
           <t>C | 584呎 (2房)
-$1202万
-$20,582/呎
-(在售)</t>
+$1022万
+$17,495/呎
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="E53" s="22" t="inlineStr">
@@ -87822,7 +87814,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -87832,7 +87824,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>239</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -88590,12 +88582,12 @@
 (26年-06月-10日)</t>
         </is>
       </c>
-      <c r="C20" s="23" t="inlineStr">
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>B | 599呎 (2房)
-招标单位
--
-(在售)</t>
+$1171万
+$19,553/呎
+(26年-09月-14日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -93290,7 +93282,7 @@
           <t>B | 628呎 (3房)
 $1189万
 $18,930/呎
-(26年-08月-24日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="D53" s="20" t="inlineStr">

--- a/files/九龙-将军澳-海瑅湾 I.xlsx
+++ b/files/九龙-将军澳-海瑅湾 I.xlsx
@@ -18955,23 +18955,23 @@
       </c>
       <c r="F279" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H279" s="5" t="n">
-        <v>11188000</v>
+        <v>9509800</v>
       </c>
       <c r="I279" s="5" t="n">
-        <v>19663</v>
+        <v>16713</v>
       </c>
       <c r="J279" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K279" s="5" t="n">
@@ -18982,7 +18982,7 @@
       </c>
       <c r="M279" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N279" s="3" t="inlineStr">
@@ -20728,14 +20728,14 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="H307" s="5" t="n">
-        <v>9675200</v>
+        <v>9452800</v>
       </c>
       <c r="I307" s="5" t="n">
-        <v>17004</v>
+        <v>16613</v>
       </c>
       <c r="J307" s="3" t="inlineStr">
         <is>
@@ -20743,10 +20743,10 @@
         </is>
       </c>
       <c r="K307" s="5" t="n">
-        <v>9675200</v>
+        <v>9452800</v>
       </c>
       <c r="L307" s="5" t="n">
-        <v>17004</v>
+        <v>16613</v>
       </c>
       <c r="M307" s="3" t="inlineStr">
         <is>
@@ -33030,7 +33030,7 @@
       </c>
       <c r="G504" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H504" s="5" t="n">
@@ -84093,7 +84093,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>97</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -84103,7 +84103,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>289</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -84323,12 +84323,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F7" s="23" t="inlineStr">
+      <c r="F7" s="22" t="inlineStr">
         <is>
           <t>E | 569呎 (2房)
-$1119万
-$19,663/呎
-(在售)</t>
+$951万
+$16,713/呎
+(26年-09月-19日)</t>
         </is>
       </c>
       <c r="G7" s="22" t="inlineStr">
@@ -84582,9 +84582,9 @@
       <c r="F11" s="22" t="inlineStr">
         <is>
           <t>E | 569呎 (2房)
-$968万
-$17,004/呎
-(26年-08月-07日)</t>
+$945万
+$16,613/呎
+(26年-07月-26日)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -86368,7 +86368,7 @@
           <t>D | 463呎 (2房)
 $814万
 $17,573/呎
-(26年-09月-07日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="F39" s="22" t="inlineStr">

--- a/files/九龙-将军澳-海瑅湾 I.xlsx
+++ b/files/九龙-将军澳-海瑅湾 I.xlsx
@@ -11870,7 +11870,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -24954,7 +24954,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H374" s="5" t="n">
@@ -26693,38 +26693,30 @@
       </c>
       <c r="F402" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H402" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I402" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="H402" s="5" t="n">
+        <v>12546000</v>
+      </c>
+      <c r="I402" s="5" t="n">
+        <v>20500</v>
       </c>
       <c r="J402" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K402" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L402" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K402" s="5" t="n">
+        <v>12546000</v>
+      </c>
+      <c r="L402" s="5" t="n">
+        <v>20500</v>
       </c>
       <c r="M402" s="3" t="inlineStr">
         <is>
@@ -26733,7 +26725,7 @@
       </c>
       <c r="N402" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -83143,7 +83135,7 @@
           <t>B | 855呎 (3房)
 $1803万
 $21,092/呎
-(26年-09月-07日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="D42" s="20" t="inlineStr">
@@ -84093,7 +84085,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>96</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -84103,7 +84095,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>290</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -85128,7 +85120,7 @@
           <t>A | 615呎 (2房)
 $1286万
 $20,912/呎
-(26年-09月-02日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -85379,12 +85371,12 @@
           <t>48</t>
         </is>
       </c>
-      <c r="B24" s="23" t="inlineStr">
+      <c r="B24" s="22" t="inlineStr">
         <is>
           <t>A | 612呎 (2房)
-招标单位
--
-(在售)</t>
+$1255万
+$20,500/呎
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">

--- a/files/九龙-将军澳-海瑅湾 I.xlsx
+++ b/files/九龙-将军澳-海瑅湾 I.xlsx
@@ -22235,34 +22235,34 @@
       </c>
       <c r="F331" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H331" s="5" t="n">
-        <v>10625000</v>
+        <v>9031200</v>
       </c>
       <c r="I331" s="5" t="n">
-        <v>23352</v>
+        <v>19849</v>
       </c>
       <c r="J331" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K331" s="5" t="n">
-        <v>9031250</v>
+        <v>9031200</v>
       </c>
       <c r="L331" s="5" t="n">
         <v>19849</v>
       </c>
       <c r="M331" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N331" s="3" t="inlineStr">
@@ -40465,23 +40465,23 @@
       </c>
       <c r="F624" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G624" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H624" s="5" t="n">
-        <v>11948000</v>
+        <v>10155800</v>
       </c>
       <c r="I624" s="5" t="n">
-        <v>20459</v>
+        <v>17390</v>
       </c>
       <c r="J624" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K624" s="5" t="n">
@@ -40492,7 +40492,7 @@
       </c>
       <c r="M624" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N624" s="3" t="inlineStr">
@@ -60361,34 +60361,34 @@
       </c>
       <c r="F940" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G940" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="H940" s="5" t="n">
-        <v>9245000</v>
+        <v>7858200</v>
       </c>
       <c r="I940" s="5" t="n">
-        <v>20454</v>
+        <v>17385</v>
       </c>
       <c r="J940" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K940" s="5" t="n">
-        <v>7858250</v>
+        <v>7858200</v>
       </c>
       <c r="L940" s="5" t="n">
-        <v>17386</v>
+        <v>17385</v>
       </c>
       <c r="M940" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N940" s="3" t="inlineStr">
@@ -81016,14 +81016,14 @@
       </c>
       <c r="G1263" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="H1263" s="5" t="n">
-        <v>7039100</v>
+        <v>7309100</v>
       </c>
       <c r="I1263" s="5" t="n">
-        <v>17003</v>
+        <v>17655</v>
       </c>
       <c r="J1263" s="3" t="inlineStr">
         <is>
@@ -81031,10 +81031,10 @@
         </is>
       </c>
       <c r="K1263" s="5" t="n">
-        <v>7039100</v>
+        <v>7309100</v>
       </c>
       <c r="L1263" s="5" t="n">
-        <v>17003</v>
+        <v>17655</v>
       </c>
       <c r="M1263" s="3" t="inlineStr">
         <is>
@@ -84085,7 +84085,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>94</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -84095,7 +84095,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>292</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -84739,12 +84739,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>B | 455呎 (2房)
-$1062万
-$23,352/呎
-(在售)</t>
+$903万
+$19,849/呎
+(26年-09月-24日)</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
@@ -87435,12 +87435,12 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="D56" s="23" t="inlineStr">
+      <c r="D56" s="22" t="inlineStr">
         <is>
           <t>C | 584呎 (2房)
-$1195万
-$20,459/呎
-(在售)</t>
+$1016万
+$17,390/呎
+(26年-09月-24日)</t>
         </is>
       </c>
       <c r="E56" s="22" t="inlineStr">
@@ -90561,7 +90561,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>56</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -90571,7 +90571,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>220</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -90708,12 +90708,12 @@
 (26年-05月-26日)</t>
         </is>
       </c>
-      <c r="F6" s="23" t="inlineStr">
+      <c r="F6" s="22" t="inlineStr">
         <is>
           <t>E | 452呎 (2房)
-$924万
-$20,454/呎
-(在售)</t>
+$786万
+$17,385/呎
+(26年-09月-26日)</t>
         </is>
       </c>
       <c r="G6" s="23" t="inlineStr">
@@ -93689,9 +93689,9 @@
       <c r="G60" s="22" t="inlineStr">
         <is>
           <t>F | 414呎 (2房)
-$704万
-$17,003/呎
-(26年-09月-10日)</t>
+$731万
+$17,655/呎
+(26年-08月-24日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-将军澳-海瑅湾 I.xlsx
+++ b/files/九龙-将军澳-海瑅湾 I.xlsx
@@ -12266,7 +12266,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -16571,38 +16571,30 @@
       </c>
       <c r="F243" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H243" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I243" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H243" s="5" t="n">
+        <v>18892000</v>
+      </c>
+      <c r="I243" s="5" t="n">
+        <v>21203</v>
       </c>
       <c r="J243" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K243" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L243" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K243" s="5" t="n">
+        <v>18892000</v>
+      </c>
+      <c r="L243" s="5" t="n">
+        <v>21203</v>
       </c>
       <c r="M243" s="3" t="inlineStr">
         <is>
@@ -16611,7 +16603,7 @@
       </c>
       <c r="N243" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -18960,7 +18952,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H279" s="5" t="n">
@@ -31782,7 +31774,7 @@
       </c>
       <c r="G484" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H484" s="5" t="n">
@@ -32216,7 +32208,7 @@
       </c>
       <c r="G491" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H491" s="5" t="n">
@@ -47105,34 +47097,34 @@
       </c>
       <c r="F728" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G728" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H728" s="5" t="n">
-        <v>10489000</v>
+        <v>8915600</v>
       </c>
       <c r="I728" s="5" t="n">
-        <v>22222</v>
+        <v>18889</v>
       </c>
       <c r="J728" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K728" s="5" t="n">
-        <v>8915650</v>
+        <v>8915600</v>
       </c>
       <c r="L728" s="5" t="n">
         <v>18889</v>
       </c>
       <c r="M728" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N728" s="3" t="inlineStr">
@@ -81454,7 +81446,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -81464,7 +81456,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>128</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -83174,7 +83166,7 @@
           <t>A | 891呎 (3房)
 $2012万
 $22,586/呎
-(26年-09月-11日)</t>
+(26年-10月-02日)</t>
         </is>
       </c>
       <c r="C43" s="23" t="inlineStr">
@@ -83780,12 +83772,12 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B56" s="23" t="inlineStr">
+      <c r="B56" s="22" t="inlineStr">
         <is>
           <t>A | 891呎 (3房)
-招标单位
--
-(在售)</t>
+$1889万
+$21,203/呎
+(26年-10月-02日)</t>
         </is>
       </c>
       <c r="C56" s="22" t="inlineStr">
@@ -84320,7 +84312,7 @@
           <t>E | 569呎 (2房)
 $951万
 $16,713/呎
-(26年-09月-19日)</t>
+(26年-10月-05日)</t>
         </is>
       </c>
       <c r="G7" s="22" t="inlineStr">
@@ -86160,7 +86152,7 @@
           <t>C | 584呎 (2房)
 $1084万
 $18,562/呎
-(26年-09月-07日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="E36" s="23" t="inlineStr">
@@ -86224,7 +86216,7 @@
           <t>C | 584呎 (2房)
 $1057万
 $18,099/呎
-(26年-09月-12日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="E37" s="23" t="inlineStr">
@@ -87806,7 +87798,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -87816,7 +87808,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>240</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -88519,12 +88511,12 @@
           <t>56</t>
         </is>
       </c>
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
-$1049万
-$22,222/呎
-(在售)</t>
+$892万
+$18,889/呎
+(26年-10月-01日)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">

--- a/files/九龙-将军澳-海瑅湾 I.xlsx
+++ b/files/九龙-将军澳-海瑅湾 I.xlsx
@@ -21785,23 +21785,23 @@
       </c>
       <c r="F324" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H324" s="5" t="n">
-        <v>10646000</v>
+        <v>9049100</v>
       </c>
       <c r="I324" s="5" t="n">
-        <v>23398</v>
+        <v>19888</v>
       </c>
       <c r="J324" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K324" s="5" t="n">
@@ -21812,7 +21812,7 @@
       </c>
       <c r="M324" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N324" s="3" t="inlineStr">
@@ -26690,7 +26690,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H402" s="5" t="n">
@@ -37850,14 +37850,14 @@
       </c>
       <c r="G582" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="H582" s="5" t="n">
-        <v>10722600</v>
+        <v>10298600</v>
       </c>
       <c r="I582" s="5" t="n">
-        <v>18361</v>
+        <v>17635</v>
       </c>
       <c r="J582" s="3" t="inlineStr">
         <is>
@@ -37865,10 +37865,10 @@
         </is>
       </c>
       <c r="K582" s="5" t="n">
-        <v>10722600</v>
+        <v>10298600</v>
       </c>
       <c r="L582" s="5" t="n">
-        <v>18361</v>
+        <v>17635</v>
       </c>
       <c r="M582" s="3" t="inlineStr">
         <is>
@@ -39152,7 +39152,7 @@
       </c>
       <c r="G603" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H603" s="5" t="n">
@@ -47350,7 +47350,7 @@
       </c>
       <c r="G732" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H732" s="5" t="n">
@@ -84077,7 +84077,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>93</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -84087,7 +84087,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>293</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -84667,12 +84667,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>B | 455呎 (2房)
-$1065万
-$23,398/呎
-(在售)</t>
+$905万
+$19,888/呎
+(26年-10月-05日)</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
@@ -85368,7 +85368,7 @@
           <t>A | 612呎 (2房)
 $1255万
 $20,500/呎
-(26年-09月-21日)</t>
+(26年-10月-08日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -87046,9 +87046,9 @@
       <c r="D50" s="22" t="inlineStr">
         <is>
           <t>C | 584呎 (2房)
-$1072万
-$18,361/呎
-(26年-07月-09日)</t>
+$1030万
+$17,635/呎
+(26年-06月-19日)</t>
         </is>
       </c>
       <c r="E50" s="22" t="inlineStr">
@@ -87240,7 +87240,7 @@
           <t>C | 584呎 (2房)
 $1022万
 $17,495/呎
-(26年-09月-15日)</t>
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="E53" s="22" t="inlineStr">
@@ -88571,7 +88571,7 @@
           <t>B | 599呎 (2房)
 $1171万
 $19,553/呎
-(26年-09月-14日)</t>
+(26年-10月-08日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">

--- a/files/九龙-将军澳-海瑅湾 I.xlsx
+++ b/files/九龙-将军澳-海瑅湾 I.xlsx
@@ -22232,7 +22232,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H331" s="5" t="n">
@@ -33076,7 +33076,7 @@
       </c>
       <c r="G505" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H505" s="5" t="n">
@@ -40462,7 +40462,7 @@
       </c>
       <c r="G624" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H624" s="5" t="n">
@@ -42039,23 +42039,23 @@
       </c>
       <c r="F649" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G649" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="H649" s="5" t="n">
-        <v>8656000</v>
+        <v>7357600</v>
       </c>
       <c r="I649" s="5" t="n">
-        <v>20561</v>
+        <v>17476</v>
       </c>
       <c r="J649" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K649" s="5" t="n">
@@ -42066,7 +42066,7 @@
       </c>
       <c r="M649" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N649" s="3" t="inlineStr">
@@ -42971,23 +42971,23 @@
       </c>
       <c r="F663" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G663" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H663" s="5" t="n">
-        <v>10766000</v>
+        <v>9151100</v>
       </c>
       <c r="I663" s="5" t="n">
-        <v>22809</v>
+        <v>19388</v>
       </c>
       <c r="J663" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K663" s="5" t="n">
@@ -42998,7 +42998,7 @@
       </c>
       <c r="M663" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N663" s="3" t="inlineStr">
@@ -84077,7 +84077,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>92</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -84087,7 +84087,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>294</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -84736,7 +84736,7 @@
           <t>B | 455呎 (2房)
 $903万
 $19,849/呎
-(26年-09月-24日)</t>
+(26年-10月-13日)</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
@@ -86344,7 +86344,7 @@
           <t>C | 584呎 (2房)
 $1053万
 $18,028/呎
-(26年-09月-16日)</t>
+(26年-10月-09日)</t>
         </is>
       </c>
       <c r="E39" s="22" t="inlineStr">
@@ -87432,7 +87432,7 @@
           <t>C | 584呎 (2房)
 $1016万
 $17,390/呎
-(26年-09月-24日)</t>
+(26年-10月-12日)</t>
         </is>
       </c>
       <c r="E56" s="22" t="inlineStr">
@@ -87707,12 +87707,12 @@
 (26年-07月-13日)</t>
         </is>
       </c>
-      <c r="G60" s="23" t="inlineStr">
+      <c r="G60" s="22" t="inlineStr">
         <is>
           <t>F | 421呎 (2房)
-$866万
-$20,561/呎
-(在售)</t>
+$736万
+$17,476/呎
+(26年-10月-10日)</t>
         </is>
       </c>
       <c r="H60" s="22" t="inlineStr">
@@ -87798,7 +87798,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -87808,7 +87808,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>241</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -87900,12 +87900,12 @@
           <t>71</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
-$1077万
-$22,809/呎
-(在售)</t>
+$915万
+$19,388/呎
+(26年-10月-08日)</t>
         </is>
       </c>
       <c r="C6" s="23" t="inlineStr">

--- a/files/九龙-将军澳-海瑅湾 I.xlsx
+++ b/files/九龙-将军澳-海瑅湾 I.xlsx
@@ -47102,7 +47102,7 @@
       </c>
       <c r="G728" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H728" s="5" t="n">
@@ -88516,7 +88516,7 @@
           <t>A | 472呎 (2房)
 $892万
 $18,889/呎
-(26年-10月-01日)</t>
+(26年-10月-14日)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">

--- a/files/九龙-将军澳-海瑅湾 I.xlsx
+++ b/files/九龙-将军澳-海瑅湾 I.xlsx
@@ -16576,7 +16576,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -21343,34 +21343,34 @@
       </c>
       <c r="F317" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H317" s="5" t="n">
-        <v>10667000</v>
+        <v>9066900</v>
       </c>
       <c r="I317" s="5" t="n">
-        <v>23444</v>
+        <v>19927</v>
       </c>
       <c r="J317" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K317" s="5" t="n">
-        <v>9066950</v>
+        <v>9066900</v>
       </c>
       <c r="L317" s="5" t="n">
         <v>19927</v>
       </c>
       <c r="M317" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N317" s="3" t="inlineStr">
@@ -21790,7 +21790,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H324" s="5" t="n">
@@ -32141,34 +32141,34 @@
       </c>
       <c r="F490" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G490" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H490" s="5" t="n">
-        <v>9609000</v>
+        <v>8167600</v>
       </c>
       <c r="I490" s="5" t="n">
-        <v>20754</v>
+        <v>17641</v>
       </c>
       <c r="J490" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K490" s="5" t="n">
-        <v>8167650</v>
+        <v>8167600</v>
       </c>
       <c r="L490" s="5" t="n">
         <v>17641</v>
       </c>
       <c r="M490" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N490" s="3" t="inlineStr">
@@ -32575,34 +32575,34 @@
       </c>
       <c r="F497" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G497" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="H497" s="5" t="n">
-        <v>9591000</v>
+        <v>8152300</v>
       </c>
       <c r="I497" s="5" t="n">
-        <v>20715</v>
+        <v>17608</v>
       </c>
       <c r="J497" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K497" s="5" t="n">
-        <v>8152350</v>
+        <v>8152300</v>
       </c>
       <c r="L497" s="5" t="n">
         <v>17608</v>
       </c>
       <c r="M497" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N497" s="3" t="inlineStr">
@@ -40899,34 +40899,34 @@
       </c>
       <c r="F631" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G631" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="H631" s="5" t="n">
-        <v>11925000</v>
+        <v>10374700</v>
       </c>
       <c r="I631" s="5" t="n">
-        <v>20420</v>
+        <v>17765</v>
       </c>
       <c r="J631" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K631" s="5" t="n">
-        <v>10136250</v>
+        <v>10374700</v>
       </c>
       <c r="L631" s="5" t="n">
-        <v>17357</v>
+        <v>17765</v>
       </c>
       <c r="M631" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N631" s="3" t="inlineStr">
@@ -60358,7 +60358,7 @@
       </c>
       <c r="G940" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H940" s="5" t="n">
@@ -81065,34 +81065,34 @@
       </c>
       <c r="F1264" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G1264" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H1264" s="5" t="n">
-        <v>8507000</v>
+        <v>7230900</v>
       </c>
       <c r="I1264" s="5" t="n">
-        <v>20400</v>
+        <v>17340</v>
       </c>
       <c r="J1264" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K1264" s="5" t="n">
-        <v>7230950</v>
+        <v>7230900</v>
       </c>
       <c r="L1264" s="5" t="n">
         <v>17340</v>
       </c>
       <c r="M1264" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N1264" s="3" t="inlineStr">
@@ -83777,7 +83777,7 @@
           <t>A | 891呎 (3房)
 $1889万
 $21,203/呎
-(26年-10月-02日)</t>
+(26年-10月-22日)</t>
         </is>
       </c>
       <c r="C56" s="22" t="inlineStr">
@@ -84077,7 +84077,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -84087,7 +84087,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>298</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -84603,12 +84603,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>B | 455呎 (2房)
-$1067万
-$23,444/呎
-(在售)</t>
+$907万
+$19,927/呎
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
@@ -84672,7 +84672,7 @@
           <t>B | 455呎 (2房)
 $905万
 $19,888/呎
-(26年-10月-05日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
@@ -86219,12 +86219,12 @@
 (26年-09月-30日)</t>
         </is>
       </c>
-      <c r="E37" s="23" t="inlineStr">
+      <c r="E37" s="22" t="inlineStr">
         <is>
           <t>D | 463呎 (2房)
-$961万
-$20,754/呎
-(在售)</t>
+$817万
+$17,641/呎
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="F37" s="22" t="inlineStr">
@@ -86283,12 +86283,12 @@
 (26年-06月-12日)</t>
         </is>
       </c>
-      <c r="E38" s="23" t="inlineStr">
+      <c r="E38" s="22" t="inlineStr">
         <is>
           <t>D | 463呎 (2房)
-$959万
-$20,715/呎
-(在售)</t>
+$815万
+$17,608/呎
+(26年-10月-24日)</t>
         </is>
       </c>
       <c r="F38" s="22" t="inlineStr">
@@ -87491,12 +87491,12 @@
 (26年-06月-24日)</t>
         </is>
       </c>
-      <c r="D57" s="23" t="inlineStr">
+      <c r="D57" s="22" t="inlineStr">
         <is>
           <t>C | 584呎 (2房)
-$1192万
-$20,420/呎
-(在售)</t>
+$1037万
+$17,765/呎
+(26年-10月-24日)</t>
         </is>
       </c>
       <c r="E57" s="22" t="inlineStr">
@@ -90553,7 +90553,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>55</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -90563,7 +90563,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>221</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -90705,7 +90705,7 @@
           <t>E | 452呎 (2房)
 $786万
 $17,385/呎
-(26年-09月-26日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="G6" s="23" t="inlineStr">
@@ -93670,12 +93670,12 @@
 (26年-07月-14日)</t>
         </is>
       </c>
-      <c r="F60" s="23" t="inlineStr">
+      <c r="F60" s="22" t="inlineStr">
         <is>
           <t>E | 417呎 (2房)
-$851万
-$20,400/呎
-(在售)</t>
+$723万
+$17,340/呎
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="G60" s="22" t="inlineStr">
